--- a/Research Logs/Matt/Matt Baker - Week 15 Research Log.xlsx
+++ b/Research Logs/Matt/Matt Baker - Week 15 Research Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RecoveryAdmin\Documents\BHB-Capstone\Research Logs\Matt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0E6242-77EB-4B81-9A5E-DE3D8BA7777B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7461242E-B7B8-471E-884E-3A0E244F8001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="2910" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research template" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="215">
   <si>
     <t>Date</t>
   </si>
@@ -754,6 +754,37 @@
   </si>
   <si>
     <t>Useful analogies, metahpors to help explanain and understand the concept, and general neural network architecture.</t>
+  </si>
+  <si>
+    <t>Week 15</t>
+  </si>
+  <si>
+    <t>More research into/sources for Mixture of experts</t>
+  </si>
+  <si>
+    <t>https://www.nvidia.com/en-us/glossary/mixture-of-experts/#nv-accordion-695d9634d2-item-92f79c7bc6</t>
+  </si>
+  <si>
+    <t>This one had good information on the comparison/contrast/use case between dense models and MoE, also good diagram.</t>
+  </si>
+  <si>
+    <t>More sources on Gemma4</t>
+  </si>
+  <si>
+    <t>https://newsletter.maartengrootendorst.com/p/a-visual-guide-to-gemma-4</t>
+  </si>
+  <si>
+    <t>Excellent illustration and descriptionn of gemma4 architecture, what makes it so efficient, layered attention focus, MTP, embedding that makes for a good source.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=L5TwuEJIxmk</t>
+  </si>
+  <si>
+    <t>AI in other Cybersecurity areas (OSINT). Maybe will have some relation to the project
+but this video looked very interesting.</t>
+  </si>
+  <si>
+    <t>AI generated images obfuscate the information landscape, making distinguishment of military asset's capabilities far more difficult. People use AI to get around copywright. How this disrupts the integrity of real investigations, and in the case of historical photos, rewrites and disturbs the historical record. His conclusion is AI can improve the productivity of very good OSINT analysts, but will be harder and harder to trust any data.</t>
   </si>
 </sst>
 </file>
@@ -1125,7 +1156,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G87"/>
+  <dimension ref="B2:G92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" style="3" customWidth="1"/>
@@ -1143,7 +1174,7 @@
       </c>
       <c r="D2" s="5">
         <f>ROUNDDOWN(SUM(C6:C499)/60,0)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -2414,6 +2445,71 @@
       </c>
       <c r="G87" t="s">
         <v>203</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B89" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="90" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B90" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C90">
+        <v>15</v>
+      </c>
+      <c r="D90" t="s">
+        <v>14</v>
+      </c>
+      <c r="E90" t="s">
+        <v>206</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G90" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B91" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C91">
+        <v>30</v>
+      </c>
+      <c r="D91" t="s">
+        <v>14</v>
+      </c>
+      <c r="E91" t="s">
+        <v>209</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="92" spans="2:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="B92" s="3">
+        <v>46316</v>
+      </c>
+      <c r="C92">
+        <v>15</v>
+      </c>
+      <c r="D92" t="s">
+        <v>9</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -2449,6 +2545,8 @@
     <hyperlink ref="G77" r:id="rId29" display="https://www.cyberdefensemagazine.com/revolutionizing-investigations-the-impact-of-ai-in-digital-forensics/_x000a_" xr:uid="{3C1EA181-AAD9-49BC-902E-99F00FE20707}"/>
     <hyperlink ref="G80" r:id="rId30" xr:uid="{E01462A6-B0A6-41B0-9B44-C56D4AA80C82}"/>
     <hyperlink ref="G86" r:id="rId31" xr:uid="{D60EDE5D-D34B-49BF-A332-0D46AAAA5D3E}"/>
+    <hyperlink ref="G91" r:id="rId32" xr:uid="{9A2EB648-19BD-4133-9EC2-F36AB9CBAA2E}"/>
+    <hyperlink ref="G92" r:id="rId33" xr:uid="{C2E75572-6AF1-420D-9550-CDD466C8170C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
